--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Money Market Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Money Market Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="221">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Money Market Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -64,10 +64,7 @@
     <t>Government Securities</t>
   </si>
   <si>
-    <t>State Government of Telangana</t>
-  </si>
-  <si>
-    <t>IN4520140075</t>
+    <t>IN0020230028</t>
   </si>
   <si>
     <t>SOV</t>
@@ -85,55 +82,46 @@
     <t>IN1520150096</t>
   </si>
   <si>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920180057</t>
+  </si>
+  <si>
+    <t>State Government of Odisha</t>
+  </si>
+  <si>
+    <t>IN2720150043</t>
+  </si>
+  <si>
+    <t>IN1520230252</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420150135</t>
+  </si>
+  <si>
+    <t>State Government of Assam</t>
+  </si>
+  <si>
+    <t>IN1220150024</t>
+  </si>
+  <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220150154</t>
+  </si>
+  <si>
     <t>State Government of Uttar Pradesh</t>
   </si>
   <si>
-    <t>IN3320140327</t>
-  </si>
-  <si>
-    <t>State Government of Madhya Pradesh</t>
-  </si>
-  <si>
-    <t>IN2120220115</t>
-  </si>
-  <si>
-    <t>State Government of Odisha</t>
-  </si>
-  <si>
-    <t>IN2720150043</t>
-  </si>
-  <si>
-    <t>State Government of West Bengal</t>
-  </si>
-  <si>
-    <t>IN3420140144</t>
-  </si>
-  <si>
-    <t>IN3420150135</t>
-  </si>
-  <si>
-    <t>State Government of Assam</t>
-  </si>
-  <si>
-    <t>IN1220150024</t>
-  </si>
-  <si>
-    <t>State Government of Uttarakhand</t>
-  </si>
-  <si>
-    <t>IN3620140035</t>
-  </si>
-  <si>
     <t>IN3320150359</t>
   </si>
   <si>
-    <t>State Government of Maharashtra</t>
-  </si>
-  <si>
-    <t>IN2220150154</t>
-  </si>
-  <si>
-    <t>IN3420140151</t>
+    <t>IN1920150068</t>
   </si>
   <si>
     <t>IN3120150161</t>
@@ -145,18 +133,9 @@
     <t>IN1020150091</t>
   </si>
   <si>
-    <t>State Government of Karnataka</t>
-  </si>
-  <si>
-    <t>IN1920150068</t>
-  </si>
-  <si>
     <t>IN3420150127</t>
   </si>
   <si>
-    <t>IN2120200273</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
@@ -187,171 +166,174 @@
     <t>Certificate of Deposits</t>
   </si>
   <si>
+    <t>Punjab National Bank **</t>
+  </si>
+  <si>
+    <t>INE160A16QT8</t>
+  </si>
+  <si>
+    <t>CRISIL A1+</t>
+  </si>
+  <si>
+    <t>INE160A16RK5</t>
+  </si>
+  <si>
+    <t>NABARD **</t>
+  </si>
+  <si>
+    <t>INE261F16900</t>
+  </si>
+  <si>
+    <t>IDBI Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE008A16X57</t>
+  </si>
+  <si>
+    <t>Small Industries Development Bank Of India. **</t>
+  </si>
+  <si>
+    <t>INE556F16AZ7</t>
+  </si>
+  <si>
+    <t>INE556F16BI1</t>
+  </si>
+  <si>
+    <t>Export-Import Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE514E16CL5</t>
+  </si>
+  <si>
+    <t>Indian Bank **</t>
+  </si>
+  <si>
+    <t>INE562A16NX4</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE238AD6AE9</t>
+  </si>
+  <si>
+    <t>INE261F16967</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE040A16GW7</t>
+  </si>
+  <si>
+    <t>INE556F16BB6</t>
+  </si>
+  <si>
+    <t>INE040A16FY5</t>
+  </si>
+  <si>
+    <t>Bank Of India **</t>
+  </si>
+  <si>
+    <t>INE084A16DI1</t>
+  </si>
+  <si>
+    <t>UCO Bank **</t>
+  </si>
+  <si>
+    <t>INE691A16LT3</t>
+  </si>
+  <si>
+    <t>INE261F16AA7</t>
+  </si>
+  <si>
+    <t>Kotak Mahindra Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE237A160Z6</t>
+  </si>
+  <si>
+    <t>INE261F16975</t>
+  </si>
+  <si>
+    <t>INE556F16BG5</t>
+  </si>
+  <si>
+    <t>IndusInd Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE095A16X85</t>
+  </si>
+  <si>
+    <t>Canara Bank **</t>
+  </si>
+  <si>
+    <t>INE476A16A16</t>
+  </si>
+  <si>
+    <t>INE084A16CZ7</t>
+  </si>
+  <si>
+    <t>INE095A16X93</t>
+  </si>
+  <si>
+    <t>INE095A16Y19</t>
+  </si>
+  <si>
+    <t>INE556F16BD2</t>
+  </si>
+  <si>
+    <t>INE084A16CY0</t>
+  </si>
+  <si>
+    <t>INE261F16959</t>
+  </si>
+  <si>
+    <t>INE562A16ON3</t>
+  </si>
+  <si>
+    <t>IDFC First Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE092T16YI0</t>
+  </si>
+  <si>
+    <t>INE476A16ZT9</t>
+  </si>
+  <si>
+    <t>INE476A16ZU7</t>
+  </si>
+  <si>
+    <t>Kotak Mahindra Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE237A163Z0</t>
+  </si>
+  <si>
     <t>HDFC Bank Ltd.</t>
   </si>
   <si>
-    <t>INE040A16FY5</t>
-  </si>
-  <si>
-    <t>CRISIL A1+</t>
-  </si>
-  <si>
-    <t>Punjab National Bank **</t>
-  </si>
-  <si>
-    <t>INE160A16QT8</t>
-  </si>
-  <si>
-    <t>Indian Bank **</t>
-  </si>
-  <si>
-    <t>INE562A16NQ8</t>
+    <t>INE040A16GJ4</t>
+  </si>
+  <si>
+    <t>INE237A166Z3</t>
+  </si>
+  <si>
+    <t>INE040A16GS5</t>
+  </si>
+  <si>
+    <t>INE556F16BH3</t>
   </si>
   <si>
     <t>Union Bank Of India **</t>
   </si>
   <si>
-    <t>INE692A16ID1</t>
+    <t>INE692A16II0</t>
   </si>
   <si>
     <t>ICRA A1+</t>
   </si>
   <si>
-    <t>NABARD **</t>
-  </si>
-  <si>
-    <t>INE261F16900</t>
-  </si>
-  <si>
-    <t>IDBI Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE008A16X57</t>
-  </si>
-  <si>
-    <t>INE562A16MZ1</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE040A16FO6</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE238AD6AE9</t>
-  </si>
-  <si>
-    <t>INE238AD6975</t>
-  </si>
-  <si>
-    <t>Kotak Mahindra Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE237A160Z6</t>
-  </si>
-  <si>
-    <t>INE238AD6942</t>
-  </si>
-  <si>
-    <t>INE562A16NX4</t>
-  </si>
-  <si>
-    <t>Canara Bank **</t>
-  </si>
-  <si>
-    <t>INE476A16ZQ5</t>
-  </si>
-  <si>
-    <t>IndusInd Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE095A16X85</t>
-  </si>
-  <si>
-    <t>Bank Of India **</t>
-  </si>
-  <si>
-    <t>INE084A16CT0</t>
-  </si>
-  <si>
-    <t>INE476A16ZO0</t>
-  </si>
-  <si>
-    <t>INE160A16QM3</t>
-  </si>
-  <si>
-    <t>INE095A16X93</t>
-  </si>
-  <si>
-    <t>INE095A16Y19</t>
-  </si>
-  <si>
-    <t>INE476A16A16</t>
-  </si>
-  <si>
-    <t>INE084A16CZ7</t>
-  </si>
-  <si>
-    <t>INE692A16HF8</t>
-  </si>
-  <si>
-    <t>INE084A16CY0</t>
-  </si>
-  <si>
-    <t>Punjab National Bank</t>
-  </si>
-  <si>
-    <t>INE160A16PE2</t>
-  </si>
-  <si>
-    <t>IDFC First Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE092T16XO0</t>
-  </si>
-  <si>
-    <t>Small Industries Development Bank Of India. **</t>
-  </si>
-  <si>
-    <t>INE556F16AS2</t>
-  </si>
-  <si>
-    <t>INE238AD6892</t>
-  </si>
-  <si>
-    <t>INE261F16819</t>
-  </si>
-  <si>
-    <t>INE476A16ZT9</t>
-  </si>
-  <si>
-    <t>INE476A16ZU7</t>
-  </si>
-  <si>
-    <t>INE556F16AY0</t>
-  </si>
-  <si>
-    <t>The Federal Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE171A16ME6</t>
-  </si>
-  <si>
-    <t>INE476A16ZL6</t>
-  </si>
-  <si>
-    <t>INE237A168X4</t>
-  </si>
-  <si>
-    <t>Union Bank Of India</t>
-  </si>
-  <si>
-    <t>INE692A16II0</t>
-  </si>
-  <si>
     <t>INE040A16GA3</t>
   </si>
   <si>
@@ -361,331 +343,271 @@
     <t>INE171A16MR8</t>
   </si>
   <si>
-    <t>INE261F16892</t>
-  </si>
-  <si>
     <t>INE092T16XZ6</t>
   </si>
   <si>
-    <t>INE095A16W94</t>
+    <t>INE238AD6AM2</t>
+  </si>
+  <si>
+    <t>INE261F16991</t>
+  </si>
+  <si>
+    <t>INE556F16BF7</t>
   </si>
   <si>
     <t>INE692A16IN0</t>
   </si>
   <si>
-    <t>INE476A16YC8</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238AD6835</t>
-  </si>
-  <si>
-    <t>INE556F16AV6</t>
-  </si>
-  <si>
-    <t>Canara Bank</t>
+    <t>Bank Of Baroda **</t>
+  </si>
+  <si>
+    <t>INE028A16HW0</t>
+  </si>
+  <si>
+    <t>FITCH A1+</t>
   </si>
   <si>
     <t>INE476A16ZW3</t>
   </si>
   <si>
-    <t>Bank Of Baroda **</t>
-  </si>
-  <si>
     <t>INE028A16HJ7</t>
   </si>
   <si>
-    <t>FITCH A1+</t>
-  </si>
-  <si>
     <t>INE692A16IK6</t>
   </si>
   <si>
-    <t>Kotak Mahindra Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE237A163Z0</t>
-  </si>
-  <si>
-    <t>INE040A16FA5</t>
-  </si>
-  <si>
-    <t>INE556F16AX2</t>
+    <t>INE261F16926</t>
+  </si>
+  <si>
+    <t>INE261F16942</t>
+  </si>
+  <si>
+    <t>INE237A165Z5</t>
+  </si>
+  <si>
+    <t>INE238AD6AN0</t>
+  </si>
+  <si>
+    <t>INE556F16BC4</t>
+  </si>
+  <si>
+    <t>INE028A16HZ3</t>
   </si>
   <si>
     <t>INE476A16ZV5</t>
   </si>
   <si>
-    <t>NABARD</t>
-  </si>
-  <si>
-    <t>INE261F16850</t>
+    <t>INE476A16A24</t>
+  </si>
+  <si>
+    <t>INE040A16GE5</t>
+  </si>
+  <si>
+    <t>Bank Of India</t>
+  </si>
+  <si>
+    <t>INE084A16DC4</t>
   </si>
   <si>
     <t>Commercial Papers</t>
   </si>
   <si>
+    <t>Can Fin Homes Ltd. **</t>
+  </si>
+  <si>
+    <t>INE477A14DV5</t>
+  </si>
+  <si>
+    <t>Bharti Telecom Ltd. **</t>
+  </si>
+  <si>
+    <t>INE403D14551</t>
+  </si>
+  <si>
+    <t>Birla Group Holdings Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE09OL14GZ5</t>
+  </si>
+  <si>
     <t>Panatone Finvest Ltd. **</t>
   </si>
   <si>
     <t>INE116F14216</t>
   </si>
   <si>
+    <t>INE09OL14HH1</t>
+  </si>
+  <si>
+    <t>Mankind Pharma Ltd **</t>
+  </si>
+  <si>
+    <t>INE634S14039</t>
+  </si>
+  <si>
     <t>Bharti Telecom Ltd.</t>
   </si>
   <si>
-    <t>INE403D14528</t>
-  </si>
-  <si>
-    <t>Export-Import Bank Of India</t>
-  </si>
-  <si>
-    <t>INE514E14SL6</t>
-  </si>
-  <si>
-    <t>Tata Teleservices Ltd. **</t>
-  </si>
-  <si>
-    <t>INE037E14AO0</t>
-  </si>
-  <si>
-    <t>Mankind Pharma Ltd **</t>
-  </si>
-  <si>
-    <t>INE634S14039</t>
-  </si>
-  <si>
-    <t>Hero Fincorp Ltd. **</t>
-  </si>
-  <si>
-    <t>INE957N14HU2</t>
-  </si>
-  <si>
     <t>INE403D14544</t>
   </si>
   <si>
-    <t>Sharekhan Ltd **</t>
-  </si>
-  <si>
-    <t>INE211H14922</t>
-  </si>
-  <si>
-    <t>Axis Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE891K14NK8</t>
+    <t>Tata Capital Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE033L14NW0</t>
+  </si>
+  <si>
+    <t>Standard Chartered Capital Ltd. **</t>
+  </si>
+  <si>
+    <t>INE403G14TH3</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE115A14FK9</t>
+  </si>
+  <si>
+    <t>Muthoot Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE414G14UK2</t>
+  </si>
+  <si>
+    <t>Julius Baer Capital (India) Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE824H14RO8</t>
+  </si>
+  <si>
+    <t>INE414G14UP1</t>
+  </si>
+  <si>
+    <t>INE033L14NQ2</t>
+  </si>
+  <si>
+    <t>INE414G14UJ4</t>
+  </si>
+  <si>
+    <t>Barclays Investments &amp; Loans (India) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE704I14JX8</t>
+  </si>
+  <si>
+    <t>IGH Holdings Pvt Ltd. **</t>
+  </si>
+  <si>
+    <t>INE02FN14440</t>
+  </si>
+  <si>
+    <t>INE414G14UN6</t>
+  </si>
+  <si>
+    <t>INE033L14OC0</t>
+  </si>
+  <si>
+    <t>INE403G14TL5</t>
+  </si>
+  <si>
+    <t>INE033L14NP4</t>
+  </si>
+  <si>
+    <t>INE115A14FI3</t>
+  </si>
+  <si>
+    <t>INE514E14SO0</t>
+  </si>
+  <si>
+    <t>Infina Finance Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE879F14KF9</t>
+  </si>
+  <si>
+    <t>SMFG India Credit Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE535H14JD0</t>
+  </si>
+  <si>
+    <t>Cholamandalam Investment And Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE121A14XQ7</t>
+  </si>
+  <si>
+    <t>INE414G14TX7</t>
+  </si>
+  <si>
+    <t>INE02FN14341</t>
+  </si>
+  <si>
+    <t>INE704I14KG1</t>
+  </si>
+  <si>
+    <t>Deutsche Investments India Pvt. Ltd. **</t>
+  </si>
+  <si>
+    <t>INE144H14HG8</t>
+  </si>
+  <si>
+    <t>INE414G14UB1</t>
+  </si>
+  <si>
+    <t>INE824H14RC3</t>
+  </si>
+  <si>
+    <t>INE414G14UI6</t>
   </si>
   <si>
     <t>Mahindra Rural Housing Finance Ltd. **</t>
   </si>
   <si>
-    <t>INE950O14BQ6</t>
-  </si>
-  <si>
-    <t>Tata Capital Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE033L14NQ2</t>
-  </si>
-  <si>
-    <t>INE950O14BR4</t>
-  </si>
-  <si>
-    <t>INE957N14IC8</t>
-  </si>
-  <si>
-    <t>INE211H14930</t>
-  </si>
-  <si>
-    <t>Tata Projects Ltd. **</t>
-  </si>
-  <si>
-    <t>INE725H14BQ6</t>
-  </si>
-  <si>
-    <t>Axis Securities Ltd. **</t>
-  </si>
-  <si>
-    <t>INE110O14DL4</t>
-  </si>
-  <si>
-    <t>Standard Chartered Capital Ltd. **</t>
-  </si>
-  <si>
-    <t>INE403G14SE2</t>
-  </si>
-  <si>
-    <t>INE403G14SW4</t>
-  </si>
-  <si>
-    <t>IGH Holdings Pvt Ltd. **</t>
-  </si>
-  <si>
-    <t>INE02FN14317</t>
-  </si>
-  <si>
-    <t>INE033L14NP4</t>
-  </si>
-  <si>
-    <t>Export-Import Bank Of India **</t>
-  </si>
-  <si>
-    <t>INE514E14SO0</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE115A14FI3</t>
-  </si>
-  <si>
-    <t>Infina Finance Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE879F14KF9</t>
-  </si>
-  <si>
-    <t>Deutsche Investments India Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE144H14HB9</t>
-  </si>
-  <si>
-    <t>Barclays Investments &amp; Loans (India) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE704I14IJ9</t>
-  </si>
-  <si>
-    <t>Birla Group Holdings Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE09OL14EP1</t>
-  </si>
-  <si>
-    <t>MINDSPACE BUSINESS PARKS REIT **</t>
-  </si>
-  <si>
-    <t>INE0CCU14039</t>
-  </si>
-  <si>
-    <t>INE403G14SC6</t>
-  </si>
-  <si>
-    <t>Tata Motors Finance Solutions Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE477S14CD7</t>
-  </si>
-  <si>
-    <t>INE02FN14267</t>
-  </si>
-  <si>
-    <t>INE09OL14EZ0</t>
-  </si>
-  <si>
-    <t>INE02FN14309</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE414G14TX7</t>
-  </si>
-  <si>
-    <t>INE02FN14341</t>
-  </si>
-  <si>
-    <t>INE414G14UB1</t>
-  </si>
-  <si>
-    <t>Julius Baer Capital (India) Pvt. Ltd. **</t>
-  </si>
-  <si>
-    <t>INE824H14RC3</t>
-  </si>
-  <si>
-    <t>HSBC Invest Direct Financial Services (India) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE790I14EU4</t>
-  </si>
-  <si>
-    <t>Nexus Select Trust **</t>
-  </si>
-  <si>
-    <t>INE0NDH14023</t>
-  </si>
-  <si>
-    <t>INE879F14JL9</t>
-  </si>
-  <si>
-    <t>INE957N14ID6</t>
-  </si>
-  <si>
-    <t>INE790I14EP4</t>
-  </si>
-  <si>
-    <t>INE09OL14EK2</t>
-  </si>
-  <si>
-    <t>INE09OL14EL0</t>
-  </si>
-  <si>
-    <t>INE09OL14EN6</t>
-  </si>
-  <si>
-    <t>INE033L14MY8</t>
-  </si>
-  <si>
-    <t>Standard Chartered Securities India Ltd **</t>
-  </si>
-  <si>
-    <t>INE472H14292</t>
-  </si>
-  <si>
-    <t>Tata Projects Ltd.</t>
-  </si>
-  <si>
-    <t>INE725H14CF7</t>
-  </si>
-  <si>
-    <t>Cholamandalam Securities Ltd. **</t>
-  </si>
-  <si>
-    <t>INE04JX14058</t>
-  </si>
-  <si>
-    <t>INE403G14SD4</t>
-  </si>
-  <si>
-    <t>INE09OL14EU1</t>
-  </si>
-  <si>
-    <t>INE414G14TY5</t>
+    <t>INE950O14BU8</t>
+  </si>
+  <si>
+    <t>INE879F14KQ6</t>
+  </si>
+  <si>
+    <t>INE879F14KU8</t>
+  </si>
+  <si>
+    <t>INE121A14XL8</t>
+  </si>
+  <si>
+    <t>INE704I14KI7</t>
   </si>
   <si>
     <t>INE144H14HL8</t>
   </si>
   <si>
+    <t>INE824H14RE9</t>
+  </si>
+  <si>
     <t>INE09OL14GH3</t>
   </si>
   <si>
     <t>INE02FN14382</t>
   </si>
   <si>
-    <t>INE824H14RE9</t>
-  </si>
-  <si>
-    <t>INE704I14IH3</t>
-  </si>
-  <si>
-    <t>INE472H14409</t>
-  </si>
-  <si>
-    <t>INE472H14318</t>
+    <t>Pilani Investment &amp; Industries Corp Ltd **</t>
+  </si>
+  <si>
+    <t>INE417C14934</t>
+  </si>
+  <si>
+    <t>INE09OL14HC2</t>
+  </si>
+  <si>
+    <t>INE414G14UM8</t>
+  </si>
+  <si>
+    <t>INE879F14KL7</t>
+  </si>
+  <si>
+    <t>INE09OL14HG3</t>
   </si>
   <si>
     <t>Bills Rediscounted</t>
@@ -697,28 +619,16 @@
     <t>364 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002023Z521</t>
-  </si>
-  <si>
-    <t>IN002023Z547</t>
-  </si>
-  <si>
-    <t>182 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002024Y241</t>
-  </si>
-  <si>
-    <t>IN002024Y209</t>
-  </si>
-  <si>
-    <t>IN002023Z513</t>
-  </si>
-  <si>
-    <t>IN002023Z539</t>
-  </si>
-  <si>
-    <t>IN002024Y225</t>
+    <t>IN002024Z487</t>
+  </si>
+  <si>
+    <t>IN002024Z479</t>
+  </si>
+  <si>
+    <t>IN002024Z495</t>
+  </si>
+  <si>
+    <t>IN002025Z021</t>
   </si>
   <si>
     <t>Units of an Alternative Investment Fund (AIF)</t>
@@ -748,7 +658,7 @@
     <t>** Non Traded / Illiquid Securities.</t>
   </si>
   <si>
-    <t>Aggregate value of investments made by other schemes of ICICI Prudential Mutual Fund are amounting to Rs. 384255.09  Lakh.</t>
+    <t>Aggregate value of investments made by other schemes of ICICI Prudential Mutual Fund are amounting to Rs. 467316.75  Lakh.</t>
   </si>
   <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
@@ -757,7 +667,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -767,9 +677,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - NIFTY Money Market Index A-I</t>
   </si>
 </sst>
 </file>
@@ -1143,13 +1050,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>191</xdr:row>
+      <xdr:row>178</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>201</xdr:row>
+      <xdr:row>188</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1167,8 +1074,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="36842700"/>
-          <a:ext cx="3657600" cy="1905000"/>
+          <a:off x="666750" y="34366200"/>
+          <a:ext cx="4019550" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1182,13 +1089,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>206</xdr:row>
+      <xdr:row>193</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>216</xdr:row>
+      <xdr:row>203</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1206,8 +1113,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="39700200"/>
-          <a:ext cx="3657600" cy="1905000"/>
+          <a:off x="666750" y="37223700"/>
+          <a:ext cx="4019550" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1540,15 +1447,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J205"/>
+  <dimension ref="B1:J191"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="54.857142857142854" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="60.285714285714285" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="17.142857142857142" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="11.142857142857142" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="12.571428571428571" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
@@ -1640,10 +1547,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>150002.71</v>
+        <v>132736.44</v>
       </c>
       <c r="H5" s="10">
-        <v>0.054247041032800015</v>
+        <v>0.0442432846068</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1677,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>150002.71</v>
+        <v>132736.44</v>
       </c>
       <c r="H7" s="10">
-        <v>0.054247041032800015</v>
+        <v>0.0442432846068</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1714,10 +1621,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>150002.71</v>
+        <v>132736.44</v>
       </c>
       <c r="H9" s="10">
-        <v>0.054247041032800015</v>
+        <v>0.0442432846068</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1728,28 +1635,28 @@
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1">
       <c r="B10" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="D10" s="14">
+        <v>6.99</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="14">
-        <v>8.08</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="F10" s="15">
-        <v>15000000</v>
+        <v>20000000</v>
       </c>
       <c r="G10" s="16">
-        <v>15013.34</v>
+        <v>20219.60</v>
       </c>
       <c r="H10" s="17">
-        <v>0.0054294303818</v>
+        <v>0.0067395322448</v>
       </c>
       <c r="I10" s="16">
-        <v>6.60</v>
+        <v>5.76</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1757,28 +1664,28 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="D11" s="14">
         <v>8.22</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" s="15">
         <v>14500000</v>
       </c>
       <c r="G11" s="16">
-        <v>14668.04</v>
+        <v>14678.36</v>
       </c>
       <c r="H11" s="17">
-        <v>0.0053045559494</v>
+        <v>0.0048925438941</v>
       </c>
       <c r="I11" s="16">
-        <v>6.90</v>
+        <v>5.87</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1786,28 +1693,28 @@
     </row>
     <row r="12" spans="2:10" ht="15" customHeight="1">
       <c r="B12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>21</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>22</v>
       </c>
       <c r="D12" s="14">
         <v>8.2</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" s="15">
         <v>14000000</v>
       </c>
       <c r="G12" s="16">
-        <v>14161.21</v>
+        <v>14170.79</v>
       </c>
       <c r="H12" s="17">
-        <v>0.0051212657421</v>
+        <v>0.004723362289</v>
       </c>
       <c r="I12" s="16">
-        <v>6.89</v>
+        <v>5.87</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1815,28 +1722,28 @@
     </row>
     <row r="13" spans="2:10" ht="15" customHeight="1">
       <c r="B13" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>24</v>
-      </c>
       <c r="D13" s="14">
-        <v>8.08</v>
+        <v>8.59</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" s="15">
         <v>14000000</v>
       </c>
       <c r="G13" s="16">
-        <v>14012.36</v>
+        <v>14160.17</v>
       </c>
       <c r="H13" s="17">
-        <v>0.0050674355676</v>
+        <v>0.0047198224647</v>
       </c>
       <c r="I13" s="16">
-        <v>6.61</v>
+        <v>5.80</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1844,28 +1751,28 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>26</v>
-      </c>
       <c r="D14" s="14">
-        <v>7.38</v>
+        <v>8.38</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" s="15">
-        <v>13738600</v>
+        <v>12500000</v>
       </c>
       <c r="G14" s="16">
-        <v>13754.88</v>
+        <v>12700.13</v>
       </c>
       <c r="H14" s="17">
-        <v>0.0049743203957</v>
+        <v>0.004233166613</v>
       </c>
       <c r="I14" s="16">
-        <v>6.62</v>
+        <v>5.92</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1873,28 +1780,28 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" s="14">
-        <v>8.38</v>
+        <v>7.25</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" s="15">
-        <v>12500000</v>
+        <v>10943400</v>
       </c>
       <c r="G15" s="16">
-        <v>12688.15</v>
+        <v>11050.57</v>
       </c>
       <c r="H15" s="17">
-        <v>0.0045885477248</v>
+        <v>0.0036833405625</v>
       </c>
       <c r="I15" s="16">
-        <v>6.89</v>
+        <v>5.83</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -1902,28 +1809,28 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="14">
-        <v>8.08</v>
+        <v>8.40</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" s="15">
-        <v>10000000</v>
+        <v>9500000</v>
       </c>
       <c r="G16" s="16">
-        <v>10008.63</v>
+        <v>9651.55</v>
       </c>
       <c r="H16" s="17">
-        <v>0.0036195250226</v>
+        <v>0.0032170237016</v>
       </c>
       <c r="I16" s="16">
-        <v>6.64</v>
+        <v>5.95</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1934,25 +1841,25 @@
         <v>29</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="14">
-        <v>8.40</v>
+        <v>8.43</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" s="15">
-        <v>9500000</v>
+        <v>7500000</v>
       </c>
       <c r="G17" s="16">
-        <v>9643.19</v>
+        <v>7622.45</v>
       </c>
       <c r="H17" s="17">
-        <v>0.0034873671524</v>
+        <v>0.0025406905952</v>
       </c>
       <c r="I17" s="16">
-        <v>6.91</v>
+        <v>5.92</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -1960,28 +1867,28 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>33</v>
-      </c>
       <c r="D18" s="14">
-        <v>8.43</v>
+        <v>8.26</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" s="15">
-        <v>7500000</v>
+        <v>6000000</v>
       </c>
       <c r="G18" s="16">
-        <v>7615.16</v>
+        <v>6080.30</v>
       </c>
       <c r="H18" s="17">
-        <v>0.0027539495586</v>
+        <v>0.0020266661016</v>
       </c>
       <c r="I18" s="16">
-        <v>6.91</v>
+        <v>5.87</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -1989,28 +1896,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="D19" s="14">
-        <v>8.08</v>
+        <v>8.34</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F19" s="15">
-        <v>6500000</v>
+        <v>5100000</v>
       </c>
       <c r="G19" s="16">
-        <v>6511.77</v>
+        <v>5175.6</v>
       </c>
       <c r="H19" s="17">
-        <v>0.0023549191504</v>
+        <v>0.0017251143982</v>
       </c>
       <c r="I19" s="16">
-        <v>6.66</v>
+        <v>5.93</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -2018,28 +1925,28 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D20" s="14">
-        <v>8.34</v>
+        <v>8.27</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" s="15">
-        <v>5100000</v>
+        <v>5000000</v>
       </c>
       <c r="G20" s="16">
-        <v>5171.28</v>
+        <v>5067.19</v>
       </c>
       <c r="H20" s="17">
-        <v>0.0018701438017</v>
+        <v>0.0016889795246</v>
       </c>
       <c r="I20" s="16">
-        <v>6.90</v>
+        <v>5.87</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -2047,28 +1954,28 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D21" s="14">
-        <v>8.26</v>
+        <v>8.27</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" s="15">
         <v>5000000</v>
       </c>
       <c r="G21" s="16">
-        <v>5062.84</v>
+        <v>5067.19</v>
       </c>
       <c r="H21" s="17">
-        <v>0.001830927516</v>
+        <v>0.0016889795246</v>
       </c>
       <c r="I21" s="16">
-        <v>6.89</v>
+        <v>5.87</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -2076,28 +1983,28 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" s="14">
-        <v>8.10</v>
+        <v>8.24</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" s="15">
-        <v>5000000</v>
+        <v>4000000</v>
       </c>
       <c r="G22" s="16">
-        <v>5009.21</v>
+        <v>4049.04</v>
       </c>
       <c r="H22" s="17">
-        <v>0.001811532741</v>
+        <v>0.0013496130309</v>
       </c>
       <c r="I22" s="16">
-        <v>6.65</v>
+        <v>5.90</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -2105,28 +2012,28 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="14">
-        <v>8.27</v>
+        <v>8.31</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23" s="15">
-        <v>4000000</v>
+        <v>3000000</v>
       </c>
       <c r="G23" s="16">
-        <v>4050.24</v>
+        <v>3043.50</v>
       </c>
       <c r="H23" s="17">
-        <v>0.0014647304403</v>
+        <v>0.001014449662</v>
       </c>
       <c r="I23" s="16">
-        <v>6.90</v>
+        <v>5.95</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -2134,57 +2041,36 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" ht="15" customHeight="1">
+      <c r="B25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="14">
-        <v>8.24</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" s="15">
-        <v>4000000</v>
-      </c>
-      <c r="G24" s="16">
-        <v>4046.54</v>
-      </c>
-      <c r="H24" s="17">
-        <v>0.0014633923708</v>
-      </c>
-      <c r="I24" s="16">
-        <v>6.92</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" ht="15" customHeight="1">
-      <c r="B25" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="14">
-        <v>8.27</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="15">
-        <v>3500000</v>
-      </c>
-      <c r="G25" s="16">
-        <v>3544.28</v>
-      </c>
-      <c r="H25" s="17">
-        <v>0.0012817548602</v>
-      </c>
-      <c r="I25" s="16">
-        <v>6.89</v>
+      <c r="H25" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>13</v>
@@ -2192,57 +2078,36 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="14">
-        <v>8.31</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F26" s="15">
-        <v>3000000</v>
-      </c>
-      <c r="G26" s="16">
-        <v>3040.91</v>
-      </c>
-      <c r="H26" s="17">
-        <v>0.0010997159288</v>
-      </c>
-      <c r="I26" s="16">
-        <v>6.91</v>
+        <v>13</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
-      <c r="B27" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="14">
-        <v>6.69</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2000000</v>
-      </c>
-      <c r="G27" s="16">
-        <v>2000.68</v>
-      </c>
-      <c r="H27" s="17">
-        <v>0.0007235267286</v>
-      </c>
-      <c r="I27" s="16">
-        <v>6.64</v>
+      <c r="B27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
@@ -2258,7 +2123,7 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>13</v>
@@ -2273,10 +2138,10 @@
         <v>13</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>13</v>
@@ -2295,7 +2160,7 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>13</v>
@@ -2310,10 +2175,10 @@
         <v>13</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I31" s="9" t="s">
         <v>13</v>
@@ -2332,7 +2197,7 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>13</v>
@@ -2347,10 +2212,10 @@
         <v>13</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>13</v>
@@ -2369,7 +2234,7 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>13</v>
@@ -2384,10 +2249,10 @@
         <v>13</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>13</v>
@@ -2406,7 +2271,7 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>13</v>
@@ -2421,10 +2286,10 @@
         <v>13</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I37" s="9" t="s">
         <v>13</v>
@@ -2443,7 +2308,7 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>13</v>
@@ -2457,11 +2322,11 @@
       <c r="F39" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>48</v>
+      <c r="G39" s="9">
+        <v>2902339.8799999985</v>
+      </c>
+      <c r="H39" s="10">
+        <v>0.9673986234506001</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>13</v>
@@ -2480,7 +2345,7 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>13</v>
@@ -2494,11 +2359,11 @@
       <c r="F41" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>48</v>
+      <c r="G41" s="9">
+        <v>1750174.6199999994</v>
+      </c>
+      <c r="H41" s="10">
+        <v>0.5833625930081</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>13</v>
@@ -2509,36 +2374,57 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>13</v>
+        <v>50</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" s="15">
+        <v>20000</v>
+      </c>
+      <c r="G42" s="16">
+        <v>96263.90</v>
+      </c>
+      <c r="H42" s="17">
+        <v>0.0320863745112</v>
+      </c>
+      <c r="I42" s="16">
+        <v>6.41</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="9">
-        <v>2603518.6100000017</v>
-      </c>
-      <c r="H43" s="10">
-        <v>0.9415375286777996</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>13</v>
+      <c r="B43" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="15">
+        <v>20000</v>
+      </c>
+      <c r="G43" s="16">
+        <v>95161.10</v>
+      </c>
+      <c r="H43" s="17">
+        <v>0.0317187927509</v>
+      </c>
+      <c r="I43" s="16">
+        <v>6.40</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2546,36 +2432,57 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>13</v>
+        <v>54</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" s="15">
+        <v>15000</v>
+      </c>
+      <c r="G44" s="16">
+        <v>72023.03</v>
+      </c>
+      <c r="H44" s="17">
+        <v>0.0240064854427</v>
+      </c>
+      <c r="I44" s="16">
+        <v>6.42</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="9">
-        <v>1594028.4999999993</v>
-      </c>
-      <c r="H45" s="10">
-        <v>0.5764651148522</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>13</v>
+      <c r="C45" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F45" s="15">
+        <v>15000</v>
+      </c>
+      <c r="G45" s="16">
+        <v>71863.73</v>
+      </c>
+      <c r="H45" s="17">
+        <v>0.0239533880774</v>
+      </c>
+      <c r="I45" s="16">
+        <v>6.56</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2583,28 +2490,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F46" s="15">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="G46" s="16">
-        <v>117475.63</v>
+        <v>71857.05</v>
       </c>
       <c r="H46" s="17">
-        <v>0.0424839345975</v>
+        <v>0.0239511615213</v>
       </c>
       <c r="I46" s="16">
-        <v>7.64</v>
+        <v>6.44</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -2612,28 +2519,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>61</v>
-      </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F47" s="15">
-        <v>20000</v>
+        <v>14000</v>
       </c>
       <c r="G47" s="16">
-        <v>93358.20</v>
+        <v>65841.93</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0337620974064</v>
+        <v>0.0219462210083</v>
       </c>
       <c r="I47" s="16">
-        <v>7.62</v>
+        <v>6.53</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2641,28 +2548,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>63</v>
-      </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F48" s="15">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="G48" s="16">
-        <v>84595.77</v>
+        <v>65786.21</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0305932486585</v>
+        <v>0.0219276485965</v>
       </c>
       <c r="I48" s="16">
-        <v>7.62</v>
+        <v>6.48</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2670,28 +2577,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>65</v>
-      </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F49" s="15">
-        <v>16000</v>
+        <v>13500</v>
       </c>
       <c r="G49" s="16">
-        <v>75193.36</v>
+        <v>64733.24</v>
       </c>
       <c r="H49" s="17">
-        <v>0.0271929572832</v>
+        <v>0.0215766760121</v>
       </c>
       <c r="I49" s="16">
-        <v>7.60</v>
+        <v>6.42</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2699,28 +2606,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F50" s="15">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="G50" s="16">
-        <v>69825.08</v>
+        <v>62556.98</v>
       </c>
       <c r="H50" s="17">
-        <v>0.0252515703213</v>
+        <v>0.0208512920063</v>
       </c>
       <c r="I50" s="16">
-        <v>7.62</v>
+        <v>6.45</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2728,28 +2635,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F51" s="15">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="G51" s="16">
-        <v>69645.9</v>
+        <v>57272.22</v>
       </c>
       <c r="H51" s="17">
-        <v>0.0251867715932</v>
+        <v>0.0190897927469</v>
       </c>
       <c r="I51" s="16">
-        <v>7.73</v>
+        <v>6.41</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -2757,28 +2664,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F52" s="15">
-        <v>14000</v>
+        <v>11500</v>
       </c>
       <c r="G52" s="16">
-        <v>68420.73</v>
+        <v>54095.94</v>
       </c>
       <c r="H52" s="17">
-        <v>0.0247437006163</v>
+        <v>0.0180310852809</v>
       </c>
       <c r="I52" s="16">
-        <v>7.59</v>
+        <v>6.53</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>13</v>
@@ -2786,28 +2693,28 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F53" s="15">
-        <v>14000</v>
+        <v>10500</v>
       </c>
       <c r="G53" s="16">
-        <v>66505.88</v>
+        <v>50105.16</v>
       </c>
       <c r="H53" s="17">
-        <v>0.0240512134837</v>
+        <v>0.0167008912863</v>
       </c>
       <c r="I53" s="16">
-        <v>7.64</v>
+        <v>6.44</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>13</v>
@@ -2815,28 +2722,28 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F54" s="15">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="G54" s="16">
-        <v>60672.24</v>
+        <v>48407.65</v>
       </c>
       <c r="H54" s="17">
-        <v>0.0219415335422</v>
+        <v>0.0161350826956</v>
       </c>
       <c r="I54" s="16">
-        <v>7.64</v>
+        <v>6.46</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -2844,28 +2751,28 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F55" s="15">
         <v>10000</v>
       </c>
       <c r="G55" s="16">
-        <v>48940.20</v>
+        <v>47538.35</v>
       </c>
       <c r="H55" s="17">
-        <v>0.0176987538265</v>
+        <v>0.0158453304067</v>
       </c>
       <c r="I55" s="16">
-        <v>7.60</v>
+        <v>6.50</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>13</v>
@@ -2873,28 +2780,28 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F56" s="15">
         <v>10000</v>
       </c>
       <c r="G56" s="16">
-        <v>46947.45</v>
+        <v>46932.15</v>
       </c>
       <c r="H56" s="17">
-        <v>0.0169780949063</v>
+        <v>0.0156432737663</v>
       </c>
       <c r="I56" s="16">
-        <v>7.58</v>
+        <v>6.74</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>13</v>
@@ -2902,28 +2809,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F57" s="15">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="G57" s="16">
-        <v>42748.20</v>
+        <v>38017.12</v>
       </c>
       <c r="H57" s="17">
-        <v>0.0154594764289</v>
+        <v>0.0126717445497</v>
       </c>
       <c r="I57" s="16">
-        <v>7.66</v>
+        <v>6.41</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>13</v>
@@ -2931,28 +2838,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F58" s="15">
-        <v>8500</v>
+        <v>7500</v>
       </c>
       <c r="G58" s="16">
-        <v>39513.44</v>
+        <v>36271.58</v>
       </c>
       <c r="H58" s="17">
-        <v>0.0142896565073</v>
+        <v>0.0120899267533</v>
       </c>
       <c r="I58" s="16">
-        <v>7.60</v>
+        <v>6.40</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
@@ -2960,28 +2867,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F59" s="15">
         <v>7000</v>
       </c>
       <c r="G59" s="16">
-        <v>32852.12</v>
+        <v>33348.49</v>
       </c>
       <c r="H59" s="17">
-        <v>0.0118806540341</v>
+        <v>0.0111156117664</v>
       </c>
       <c r="I59" s="16">
-        <v>7.60</v>
+        <v>6.41</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -2989,28 +2896,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F60" s="15">
-        <v>6500</v>
+        <v>7000</v>
       </c>
       <c r="G60" s="16">
-        <v>30519.58</v>
+        <v>33253.61</v>
       </c>
       <c r="H60" s="17">
-        <v>0.0110371133201</v>
+        <v>0.011083986669</v>
       </c>
       <c r="I60" s="16">
-        <v>7.72</v>
+        <v>6.43</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -3018,28 +2925,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F61" s="15">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="G61" s="16">
-        <v>29291.13</v>
+        <v>31403.16</v>
       </c>
       <c r="H61" s="17">
-        <v>0.0105928561626</v>
+        <v>0.0104672006078</v>
       </c>
       <c r="I61" s="16">
-        <v>7.62</v>
+        <v>6.82</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -3047,28 +2954,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F62" s="15">
         <v>6000</v>
       </c>
       <c r="G62" s="16">
-        <v>28203.03</v>
+        <v>28772.16</v>
       </c>
       <c r="H62" s="17">
-        <v>0.0101993552362</v>
+        <v>0.0095902441232</v>
       </c>
       <c r="I62" s="16">
-        <v>7.60</v>
+        <v>6.41</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>13</v>
@@ -3076,28 +2983,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F63" s="15">
         <v>6000</v>
       </c>
       <c r="G63" s="16">
-        <v>28191.96</v>
+        <v>28754.73</v>
       </c>
       <c r="H63" s="17">
-        <v>0.0101953518769</v>
+        <v>0.0095844344115</v>
       </c>
       <c r="I63" s="16">
-        <v>7.63</v>
+        <v>6.51</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>13</v>
@@ -3105,28 +3012,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F64" s="15">
         <v>6000</v>
       </c>
       <c r="G64" s="16">
-        <v>27923.28</v>
+        <v>28748.85</v>
       </c>
       <c r="H64" s="17">
-        <v>0.0100981863325</v>
+        <v>0.0095824745087</v>
       </c>
       <c r="I64" s="16">
-        <v>7.69</v>
+        <v>6.82</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>13</v>
@@ -3134,28 +3041,28 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F65" s="15">
         <v>6000</v>
       </c>
       <c r="G65" s="16">
-        <v>27906.87</v>
+        <v>28733.43</v>
       </c>
       <c r="H65" s="17">
-        <v>0.0100922518134</v>
+        <v>0.0095773347638</v>
       </c>
       <c r="I65" s="16">
-        <v>7.69</v>
+        <v>6.82</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>13</v>
@@ -3163,28 +3070,28 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F66" s="15">
         <v>6000</v>
       </c>
       <c r="G66" s="16">
-        <v>27894.42</v>
+        <v>28574.88</v>
       </c>
       <c r="H66" s="17">
-        <v>0.0100877493903</v>
+        <v>0.0095244873861</v>
       </c>
       <c r="I66" s="16">
-        <v>7.59</v>
+        <v>6.43</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>13</v>
@@ -3192,28 +3099,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F67" s="15">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="G67" s="16">
-        <v>27878.94</v>
+        <v>26512.67</v>
       </c>
       <c r="H67" s="17">
-        <v>0.0100821511968</v>
+        <v>0.0088371181607</v>
       </c>
       <c r="I67" s="16">
-        <v>7.65</v>
+        <v>6.54</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>13</v>
@@ -3221,28 +3128,28 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F68" s="15">
         <v>5500</v>
       </c>
       <c r="G68" s="16">
-        <v>27212.35</v>
+        <v>26293.88</v>
       </c>
       <c r="H68" s="17">
-        <v>0.0098410853182</v>
+        <v>0.0087641917794</v>
       </c>
       <c r="I68" s="16">
-        <v>7.28</v>
+        <v>6.41</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>13</v>
@@ -3250,28 +3157,28 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F69" s="15">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="G69" s="16">
-        <v>25727.87</v>
+        <v>23760.70</v>
       </c>
       <c r="H69" s="17">
-        <v>0.0093042373674</v>
+        <v>0.0079198403435</v>
       </c>
       <c r="I69" s="16">
-        <v>7.67</v>
+        <v>6.41</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>13</v>
@@ -3279,28 +3186,28 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F70" s="15">
         <v>5000</v>
       </c>
       <c r="G70" s="16">
-        <v>24695.55</v>
+        <v>23461.68</v>
       </c>
       <c r="H70" s="17">
-        <v>0.0089309087429</v>
+        <v>0.0078201719558</v>
       </c>
       <c r="I70" s="16">
-        <v>7.50</v>
+        <v>6.69</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>13</v>
@@ -3308,28 +3215,28 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F71" s="15">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="G71" s="16">
-        <v>24366.90</v>
+        <v>19317.28</v>
       </c>
       <c r="H71" s="17">
-        <v>0.0088120556233</v>
+        <v>0.0064387738354</v>
       </c>
       <c r="I71" s="16">
-        <v>7.71</v>
+        <v>6.45</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
@@ -3337,28 +3244,28 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F72" s="15">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="G72" s="16">
-        <v>24341.25</v>
+        <v>19313.98</v>
       </c>
       <c r="H72" s="17">
-        <v>0.0088027795468</v>
+        <v>0.00643767389</v>
       </c>
       <c r="I72" s="16">
-        <v>7.66</v>
+        <v>6.45</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>13</v>
@@ -3366,28 +3273,28 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F73" s="15">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="G73" s="16">
-        <v>23913.18</v>
+        <v>19189.42</v>
       </c>
       <c r="H73" s="17">
-        <v>0.008647972138</v>
+        <v>0.0063961559501</v>
       </c>
       <c r="I73" s="16">
-        <v>7.68</v>
+        <v>6.40</v>
       </c>
       <c r="J73" s="11" t="s">
         <v>13</v>
@@ -3395,28 +3302,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D74" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F74" s="15">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="G74" s="16">
-        <v>22390.72</v>
+        <v>19093.78</v>
       </c>
       <c r="H74" s="17">
-        <v>0.0080973890846</v>
+        <v>0.006364277532</v>
       </c>
       <c r="I74" s="16">
-        <v>7.13</v>
+        <v>6.44</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>13</v>
@@ -3424,28 +3331,28 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F75" s="15">
         <v>4000</v>
       </c>
       <c r="G75" s="16">
-        <v>18750.64</v>
+        <v>19093.78</v>
       </c>
       <c r="H75" s="17">
-        <v>0.0067809890734</v>
+        <v>0.006364277532</v>
       </c>
       <c r="I75" s="16">
-        <v>7.60</v>
+        <v>6.39</v>
       </c>
       <c r="J75" s="11" t="s">
         <v>13</v>
@@ -3453,28 +3360,28 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D76" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F76" s="15">
         <v>4000</v>
       </c>
       <c r="G76" s="16">
-        <v>18746.98</v>
+        <v>19008.80</v>
       </c>
       <c r="H76" s="17">
-        <v>0.0067796654695</v>
+        <v>0.0063359522708</v>
       </c>
       <c r="I76" s="16">
-        <v>7.60</v>
+        <v>6.43</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>13</v>
@@ -3482,28 +3389,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D77" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F77" s="15">
         <v>4000</v>
       </c>
       <c r="G77" s="16">
-        <v>18652.66</v>
+        <v>18859.58</v>
       </c>
       <c r="H77" s="17">
-        <v>0.0067455555463</v>
+        <v>0.0062862147389</v>
       </c>
       <c r="I77" s="16">
-        <v>7.62</v>
+        <v>6.53</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>13</v>
@@ -3511,28 +3418,28 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="F78" s="15">
         <v>3000</v>
       </c>
       <c r="G78" s="16">
-        <v>14658.21</v>
+        <v>14488.92</v>
       </c>
       <c r="H78" s="17">
-        <v>0.0053010010242</v>
+        <v>0.0048294003607</v>
       </c>
       <c r="I78" s="16">
-        <v>7.67</v>
+        <v>6.44</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>13</v>
@@ -3540,28 +3447,28 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D79" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F79" s="15">
         <v>3000</v>
       </c>
       <c r="G79" s="16">
-        <v>14648.87</v>
+        <v>14487.57</v>
       </c>
       <c r="H79" s="17">
-        <v>0.0052976233028</v>
+        <v>0.004828950383</v>
       </c>
       <c r="I79" s="16">
-        <v>7.54</v>
+        <v>6.46</v>
       </c>
       <c r="J79" s="11" t="s">
         <v>13</v>
@@ -3569,28 +3476,28 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F80" s="15">
         <v>3000</v>
       </c>
       <c r="G80" s="16">
-        <v>14619.50</v>
+        <v>14411.94</v>
       </c>
       <c r="H80" s="17">
-        <v>0.0052870019241</v>
+        <v>0.0048037416339</v>
       </c>
       <c r="I80" s="16">
-        <v>7.60</v>
+        <v>6.59</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>13</v>
@@ -3598,28 +3505,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F81" s="15">
         <v>3000</v>
       </c>
       <c r="G81" s="16">
-        <v>14062.98</v>
+        <v>14370.90</v>
       </c>
       <c r="H81" s="17">
-        <v>0.005085741805</v>
+        <v>0.0047900623126</v>
       </c>
       <c r="I81" s="16">
-        <v>7.60</v>
+        <v>6.63</v>
       </c>
       <c r="J81" s="11" t="s">
         <v>13</v>
@@ -3627,28 +3534,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F82" s="15">
         <v>3000</v>
       </c>
       <c r="G82" s="16">
-        <v>14059.08</v>
+        <v>14370.71</v>
       </c>
       <c r="H82" s="17">
-        <v>0.0050843314074</v>
+        <v>0.0047899989825</v>
       </c>
       <c r="I82" s="16">
-        <v>7.63</v>
+        <v>6.45</v>
       </c>
       <c r="J82" s="11" t="s">
         <v>13</v>
@@ -3656,28 +3563,28 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D83" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F83" s="15">
         <v>3000</v>
       </c>
       <c r="G83" s="16">
-        <v>13983.32</v>
+        <v>14258.81</v>
       </c>
       <c r="H83" s="17">
-        <v>0.0050569335302</v>
+        <v>0.0047527008332</v>
       </c>
       <c r="I83" s="16">
-        <v>7.67</v>
+        <v>6.41</v>
       </c>
       <c r="J83" s="11" t="s">
         <v>13</v>
@@ -3685,28 +3592,28 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D84" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F84" s="15">
         <v>3000</v>
       </c>
       <c r="G84" s="16">
-        <v>13970.45</v>
+        <v>14253.93</v>
       </c>
       <c r="H84" s="17">
-        <v>0.0050522792182</v>
+        <v>0.0047510742473</v>
       </c>
       <c r="I84" s="16">
-        <v>7.62</v>
+        <v>6.43</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>13</v>
@@ -3714,28 +3621,28 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D85" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="F85" s="15">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G85" s="16">
-        <v>13939.14</v>
+        <v>11989.28</v>
       </c>
       <c r="H85" s="17">
-        <v>0.0050409562571</v>
+        <v>0.0039962283701</v>
       </c>
       <c r="I85" s="16">
-        <v>7.70</v>
+        <v>6.43</v>
       </c>
       <c r="J85" s="11" t="s">
         <v>13</v>
@@ -3743,28 +3650,28 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D86" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F86" s="15">
         <v>2500</v>
       </c>
       <c r="G86" s="16">
-        <v>12006.40</v>
+        <v>11920.30</v>
       </c>
       <c r="H86" s="17">
-        <v>0.0043419993776</v>
+        <v>0.0039732361776</v>
       </c>
       <c r="I86" s="16">
-        <v>7.74</v>
+        <v>6.39</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>13</v>
@@ -3772,28 +3679,28 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
       <c r="B87" s="12" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D87" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F87" s="15">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="G87" s="16">
-        <v>11624.93</v>
+        <v>9645.47</v>
       </c>
       <c r="H87" s="17">
-        <v>0.0042040444117</v>
+        <v>0.0032149971355</v>
       </c>
       <c r="I87" s="16">
-        <v>7.59</v>
+        <v>6.45</v>
       </c>
       <c r="J87" s="11" t="s">
         <v>13</v>
@@ -3801,28 +3708,28 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D88" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F88" s="15">
         <v>2000</v>
       </c>
       <c r="G88" s="16">
-        <v>9893.73</v>
+        <v>9625.60</v>
       </c>
       <c r="H88" s="17">
-        <v>0.0035779725398</v>
+        <v>0.0032083741308</v>
       </c>
       <c r="I88" s="16">
-        <v>7.26</v>
+        <v>6.40</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>13</v>
@@ -3830,28 +3737,28 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
       <c r="B89" s="12" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="F89" s="15">
         <v>2000</v>
       </c>
       <c r="G89" s="16">
-        <v>9744.37</v>
+        <v>9612.52</v>
       </c>
       <c r="H89" s="17">
-        <v>0.0035239579287</v>
+        <v>0.0032040143471</v>
       </c>
       <c r="I89" s="16">
-        <v>7.66</v>
+        <v>6.43</v>
       </c>
       <c r="J89" s="11" t="s">
         <v>13</v>
@@ -3859,28 +3766,28 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
       <c r="B90" s="12" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D90" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F90" s="15">
         <v>2000</v>
       </c>
       <c r="G90" s="16">
-        <v>9476.51</v>
+        <v>9582.34</v>
       </c>
       <c r="H90" s="17">
-        <v>0.0034270889294</v>
+        <v>0.0031939548463</v>
       </c>
       <c r="I90" s="16">
-        <v>7.64</v>
+        <v>6.41</v>
       </c>
       <c r="J90" s="11" t="s">
         <v>13</v>
@@ -3888,28 +3795,28 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
       <c r="B91" s="12" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F91" s="15">
         <v>2000</v>
       </c>
       <c r="G91" s="16">
-        <v>9360.7</v>
+        <v>9579.11</v>
       </c>
       <c r="H91" s="17">
-        <v>0.0033852073539</v>
+        <v>0.0031928782331</v>
       </c>
       <c r="I91" s="16">
-        <v>7.60</v>
+        <v>6.41</v>
       </c>
       <c r="J91" s="11" t="s">
         <v>13</v>
@@ -3917,28 +3824,28 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
       <c r="B92" s="12" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D92" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="F92" s="15">
         <v>2000</v>
       </c>
       <c r="G92" s="16">
-        <v>9337.07</v>
+        <v>9561.28</v>
       </c>
       <c r="H92" s="17">
-        <v>0.0033766617911</v>
+        <v>0.0031869351946</v>
       </c>
       <c r="I92" s="16">
-        <v>7.58</v>
+        <v>6.39</v>
       </c>
       <c r="J92" s="11" t="s">
         <v>13</v>
@@ -3946,28 +3853,28 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
       <c r="B93" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F93" s="15">
         <v>2000</v>
       </c>
       <c r="G93" s="16">
-        <v>9323.38</v>
+        <v>9535.64</v>
       </c>
       <c r="H93" s="17">
-        <v>0.0033717109339</v>
+        <v>0.003178388952</v>
       </c>
       <c r="I93" s="16">
-        <v>7.59</v>
+        <v>6.44</v>
       </c>
       <c r="J93" s="11" t="s">
         <v>13</v>
@@ -3975,28 +3882,28 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D94" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F94" s="15">
         <v>2000</v>
       </c>
       <c r="G94" s="16">
-        <v>9304.3</v>
+        <v>9532.96</v>
       </c>
       <c r="H94" s="17">
-        <v>0.003364810835</v>
+        <v>0.003177495663</v>
       </c>
       <c r="I94" s="16">
-        <v>7.56</v>
+        <v>6.43</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>13</v>
@@ -4004,28 +3911,28 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
       <c r="B95" s="12" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D95" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F95" s="15">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G95" s="16">
-        <v>4854.20</v>
+        <v>9528.29</v>
       </c>
       <c r="H95" s="17">
-        <v>0.0017554748616</v>
+        <v>0.0031759390736</v>
       </c>
       <c r="I95" s="16">
-        <v>7.67</v>
+        <v>6.39</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>13</v>
@@ -4033,28 +3940,28 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D96" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F96" s="15">
         <v>1000</v>
       </c>
       <c r="G96" s="16">
-        <v>4698.20</v>
+        <v>4826.03</v>
       </c>
       <c r="H96" s="17">
-        <v>0.0016990589582</v>
+        <v>0.0016085968466</v>
       </c>
       <c r="I96" s="16">
-        <v>7.64</v>
+        <v>6.45</v>
       </c>
       <c r="J96" s="11" t="s">
         <v>13</v>
@@ -4062,28 +3969,28 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
       <c r="B97" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D97" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F97" s="15">
         <v>1000</v>
       </c>
       <c r="G97" s="16">
-        <v>4684.01</v>
+        <v>4792.29</v>
       </c>
       <c r="H97" s="17">
-        <v>0.0016939272808</v>
+        <v>0.0015973507379</v>
       </c>
       <c r="I97" s="16">
-        <v>7.60</v>
+        <v>6.41</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>13</v>
@@ -4091,28 +3998,28 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
       <c r="B98" s="12" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F98" s="15">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G98" s="16">
-        <v>2477.64</v>
+        <v>4791.64</v>
       </c>
       <c r="H98" s="17">
-        <v>0.0008960147369</v>
+        <v>0.001597134082</v>
       </c>
       <c r="I98" s="16">
-        <v>7.32</v>
+        <v>6.40</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
@@ -4120,35 +4027,35 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
-        <v>13</v>
+        <v>129</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F99" s="15">
+        <v>1000</v>
+      </c>
+      <c r="G99" s="16">
+        <v>4786.89</v>
+      </c>
+      <c r="H99" s="17">
+        <v>0.0015955508272</v>
+      </c>
+      <c r="I99" s="16">
+        <v>6.50</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G100" s="9">
-        <v>756000.8600000003</v>
-      </c>
-      <c r="H100" s="10">
-        <v>0.2734004583897999</v>
-      </c>
-      <c r="I100" s="9" t="s">
+      <c r="B100" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J100" s="11" t="s">
@@ -4156,29 +4063,29 @@
       </c>
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
-      <c r="B101" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="C101" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F101" s="15">
-        <v>10000</v>
-      </c>
-      <c r="G101" s="16">
-        <v>46453</v>
-      </c>
-      <c r="H101" s="17">
-        <v>0.0167992818073</v>
-      </c>
-      <c r="I101" s="16">
-        <v>8.06</v>
+      <c r="B101" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="9">
+        <v>850377.70</v>
+      </c>
+      <c r="H101" s="10">
+        <v>0.28344516852050017</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
@@ -4186,28 +4093,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D102" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="F102" s="15">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="G102" s="16">
-        <v>39792.84</v>
+        <v>71456.1</v>
       </c>
       <c r="H102" s="17">
-        <v>0.0143906988369</v>
+        <v>0.0238175181528</v>
       </c>
       <c r="I102" s="16">
-        <v>7.60</v>
+        <v>6.78</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
@@ -4215,28 +4122,28 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="12" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F103" s="15">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="G103" s="16">
-        <v>39012.88</v>
+        <v>71405.18</v>
       </c>
       <c r="H103" s="17">
-        <v>0.0141086337854</v>
+        <v>0.0238005456616</v>
       </c>
       <c r="I103" s="16">
-        <v>7.57</v>
+        <v>7.15</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
@@ -4244,28 +4151,28 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
       <c r="B104" s="12" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D104" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F104" s="15">
-        <v>6700</v>
+        <v>10500</v>
       </c>
       <c r="G104" s="16">
-        <v>33409.62</v>
+        <v>49770.84</v>
       </c>
       <c r="H104" s="17">
-        <v>0.0120822685608</v>
+        <v>0.0165894568158</v>
       </c>
       <c r="I104" s="16">
-        <v>7.59</v>
+        <v>7.05</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
@@ -4273,28 +4180,28 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
       <c r="B105" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D105" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F105" s="15">
-        <v>6600</v>
+        <v>10000</v>
       </c>
       <c r="G105" s="16">
-        <v>31243.21</v>
+        <v>47952.80</v>
       </c>
       <c r="H105" s="17">
-        <v>0.0112988071675</v>
+        <v>0.0159834735519</v>
       </c>
       <c r="I105" s="16">
-        <v>7.96</v>
+        <v>6.89</v>
       </c>
       <c r="J105" s="11" t="s">
         <v>13</v>
@@ -4302,28 +4209,28 @@
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
       <c r="B106" s="12" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D106" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F106" s="15">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="G106" s="16">
-        <v>29890.32</v>
+        <v>32734.84</v>
       </c>
       <c r="H106" s="17">
-        <v>0.0108095474778</v>
+        <v>0.0109110719158</v>
       </c>
       <c r="I106" s="16">
-        <v>7.88</v>
+        <v>7.16</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
@@ -4331,28 +4238,28 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
       <c r="B107" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F107" s="15">
-        <v>6000</v>
+        <v>6600</v>
       </c>
       <c r="G107" s="16">
-        <v>28348.83</v>
+        <v>32178.80</v>
       </c>
       <c r="H107" s="17">
-        <v>0.0102520824075</v>
+        <v>0.0107257344458</v>
       </c>
       <c r="I107" s="16">
-        <v>8.24</v>
+        <v>6.75</v>
       </c>
       <c r="J107" s="11" t="s">
         <v>13</v>
@@ -4360,28 +4267,28 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
       <c r="B108" s="12" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D108" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F108" s="15">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="G108" s="16">
-        <v>24947.08</v>
+        <v>29209.29</v>
       </c>
       <c r="H108" s="17">
-        <v>0.0090218721544</v>
+        <v>0.0097359468933</v>
       </c>
       <c r="I108" s="16">
-        <v>8.61</v>
+        <v>7.16</v>
       </c>
       <c r="J108" s="11" t="s">
         <v>13</v>
@@ -4389,28 +4296,28 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
       <c r="B109" s="12" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D109" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F109" s="15">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="G109" s="16">
-        <v>24737.08</v>
+        <v>28521.93</v>
       </c>
       <c r="H109" s="17">
-        <v>0.008945927669</v>
+        <v>0.0095068382619</v>
       </c>
       <c r="I109" s="16">
-        <v>7.61</v>
+        <v>6.55</v>
       </c>
       <c r="J109" s="11" t="s">
         <v>13</v>
@@ -4418,28 +4325,28 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="12" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C110" s="13" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D110" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F110" s="15">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="G110" s="16">
-        <v>19843.62</v>
+        <v>28425.78</v>
       </c>
       <c r="H110" s="17">
-        <v>0.007176254805</v>
+        <v>0.0094747898522</v>
       </c>
       <c r="I110" s="16">
-        <v>7.57</v>
+        <v>7.12</v>
       </c>
       <c r="J110" s="11" t="s">
         <v>13</v>
@@ -4447,28 +4354,28 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D111" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F111" s="15">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G111" s="16">
-        <v>18599.52</v>
+        <v>23792.63</v>
       </c>
       <c r="H111" s="17">
-        <v>0.0067263379751</v>
+        <v>0.0079304831487</v>
       </c>
       <c r="I111" s="16">
-        <v>7.72</v>
+        <v>6.55</v>
       </c>
       <c r="J111" s="11" t="s">
         <v>13</v>
@@ -4476,28 +4383,28 @@
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
       <c r="B112" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D112" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F112" s="15">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="G112" s="16">
-        <v>17409.02</v>
+        <v>23723.98</v>
       </c>
       <c r="H112" s="17">
-        <v>0.0062958050711</v>
+        <v>0.0079076009508</v>
       </c>
       <c r="I112" s="16">
-        <v>7.63</v>
+        <v>7.17</v>
       </c>
       <c r="J112" s="11" t="s">
         <v>13</v>
@@ -4505,28 +4412,28 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
       <c r="B113" s="12" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D113" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F113" s="15">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="G113" s="16">
-        <v>17402.32</v>
+        <v>23669.33</v>
       </c>
       <c r="H113" s="17">
-        <v>0.0062933820804</v>
+        <v>0.0078893851881</v>
       </c>
       <c r="I113" s="16">
-        <v>7.88</v>
+        <v>7.20</v>
       </c>
       <c r="J113" s="11" t="s">
         <v>13</v>
@@ -4534,28 +4441,28 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
       <c r="B114" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D114" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F114" s="15">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="G114" s="16">
-        <v>14993.36</v>
+        <v>21070.24</v>
       </c>
       <c r="H114" s="17">
-        <v>0.0054222048065</v>
+        <v>0.0070230648423</v>
       </c>
       <c r="I114" s="16">
-        <v>8.10</v>
+        <v>7.20</v>
       </c>
       <c r="J114" s="11" t="s">
         <v>13</v>
@@ -4563,28 +4470,28 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="12" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D115" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F115" s="15">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G115" s="16">
-        <v>14948.07</v>
+        <v>19186.22</v>
       </c>
       <c r="H115" s="17">
-        <v>0.0054058261125</v>
+        <v>0.0063950893364</v>
       </c>
       <c r="I115" s="16">
-        <v>7.46</v>
+        <v>6.56</v>
       </c>
       <c r="J115" s="11" t="s">
         <v>13</v>
@@ -4592,28 +4499,28 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
       <c r="B116" s="12" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D116" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F116" s="15">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G116" s="16">
-        <v>14927.46</v>
+        <v>19021.70</v>
       </c>
       <c r="H116" s="17">
-        <v>0.0053983727037</v>
+        <v>0.0063402520575</v>
       </c>
       <c r="I116" s="16">
-        <v>7.71</v>
+        <v>7.17</v>
       </c>
       <c r="J116" s="11" t="s">
         <v>13</v>
@@ -4621,28 +4528,28 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
       <c r="B117" s="12" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D117" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F117" s="15">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G117" s="16">
-        <v>14917.76</v>
+        <v>18960.70</v>
       </c>
       <c r="H117" s="17">
-        <v>0.0053948647918</v>
+        <v>0.006319919733</v>
       </c>
       <c r="I117" s="16">
-        <v>7.74</v>
+        <v>7.12</v>
       </c>
       <c r="J117" s="11" t="s">
         <v>13</v>
@@ -4650,28 +4557,28 @@
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
       <c r="B118" s="12" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D118" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F118" s="15">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G118" s="16">
-        <v>14620.55</v>
+        <v>18944.70</v>
       </c>
       <c r="H118" s="17">
-        <v>0.0052873816465</v>
+        <v>0.0063145866643</v>
       </c>
       <c r="I118" s="16">
-        <v>8.24</v>
+        <v>7.21</v>
       </c>
       <c r="J118" s="11" t="s">
         <v>13</v>
@@ -4679,28 +4586,28 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="12" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F119" s="15">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G119" s="16">
-        <v>14612.97</v>
+        <v>18943.9</v>
       </c>
       <c r="H119" s="17">
-        <v>0.0052846404122</v>
+        <v>0.0063143200109</v>
       </c>
       <c r="I119" s="16">
-        <v>8.26</v>
+        <v>7.17</v>
       </c>
       <c r="J119" s="11" t="s">
         <v>13</v>
@@ -4708,28 +4615,28 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C120" s="13" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D120" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F120" s="15">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="G120" s="16">
-        <v>13968.89</v>
+        <v>18788.46</v>
       </c>
       <c r="H120" s="17">
-        <v>0.0050517150592</v>
+        <v>0.0062625092485</v>
       </c>
       <c r="I120" s="16">
-        <v>7.72</v>
+        <v>6.63</v>
       </c>
       <c r="J120" s="11" t="s">
         <v>13</v>
@@ -4737,28 +4644,28 @@
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
       <c r="B121" s="12" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D121" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F121" s="15">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="G121" s="16">
-        <v>13955.31</v>
+        <v>16736.34</v>
       </c>
       <c r="H121" s="17">
-        <v>0.0050468039824</v>
+        <v>0.0055785031895</v>
       </c>
       <c r="I121" s="16">
-        <v>7.59</v>
+        <v>7.12</v>
       </c>
       <c r="J121" s="11" t="s">
         <v>13</v>
@@ -4766,28 +4673,28 @@
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
       <c r="B122" s="12" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="C122" s="13" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D122" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F122" s="15">
         <v>3000</v>
       </c>
       <c r="G122" s="16">
-        <v>13955.13</v>
+        <v>14407.05</v>
       </c>
       <c r="H122" s="17">
-        <v>0.0050467388872</v>
+        <v>0.0048021117147</v>
       </c>
       <c r="I122" s="16">
-        <v>7.72</v>
+        <v>6.56</v>
       </c>
       <c r="J122" s="11" t="s">
         <v>13</v>
@@ -4795,28 +4702,28 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
       <c r="B123" s="12" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F123" s="15">
         <v>3000</v>
       </c>
       <c r="G123" s="16">
-        <v>13905.42</v>
+        <v>14394.63</v>
       </c>
       <c r="H123" s="17">
-        <v>0.0050287617425</v>
+        <v>0.0047979719202</v>
       </c>
       <c r="I123" s="16">
-        <v>8.28</v>
+        <v>6.56</v>
       </c>
       <c r="J123" s="11" t="s">
         <v>13</v>
@@ -4824,28 +4731,28 @@
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
       <c r="B124" s="12" t="s">
-        <v>177</v>
+        <v>61</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="D124" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F124" s="15">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G124" s="16">
-        <v>9966.19</v>
+        <v>14392.44</v>
       </c>
       <c r="H124" s="17">
-        <v>0.0036041770037</v>
+        <v>0.0047972419564</v>
       </c>
       <c r="I124" s="16">
-        <v>7.74</v>
+        <v>6.42</v>
       </c>
       <c r="J124" s="11" t="s">
         <v>13</v>
@@ -4853,28 +4760,28 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1">
       <c r="B125" s="12" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="D125" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F125" s="15">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G125" s="16">
-        <v>9959.87</v>
+        <v>14359.68</v>
       </c>
       <c r="H125" s="17">
-        <v>0.0036018914363</v>
+        <v>0.0047863224982</v>
       </c>
       <c r="I125" s="16">
-        <v>7.74</v>
+        <v>7.17</v>
       </c>
       <c r="J125" s="11" t="s">
         <v>13</v>
@@ -4882,28 +4789,28 @@
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1">
       <c r="B126" s="12" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D126" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F126" s="15">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G126" s="16">
-        <v>9957.42</v>
+        <v>14316.54</v>
       </c>
       <c r="H126" s="17">
-        <v>0.0036010054173</v>
+        <v>0.0047719432117</v>
       </c>
       <c r="I126" s="16">
-        <v>7.81</v>
+        <v>6.97</v>
       </c>
       <c r="J126" s="11" t="s">
         <v>13</v>
@@ -4911,28 +4818,28 @@
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1">
       <c r="B127" s="12" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D127" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E127" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F127" s="15">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="G127" s="16">
-        <v>9950.18</v>
+        <v>11671.74</v>
       </c>
       <c r="H127" s="17">
-        <v>0.0035983871408</v>
+        <v>0.0038903869554</v>
       </c>
       <c r="I127" s="16">
-        <v>7.62</v>
+        <v>7.18</v>
       </c>
       <c r="J127" s="11" t="s">
         <v>13</v>
@@ -4940,28 +4847,28 @@
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1">
       <c r="B128" s="12" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D128" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E128" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F128" s="15">
         <v>2000</v>
       </c>
       <c r="G128" s="16">
-        <v>9934.82</v>
+        <v>9676.19</v>
       </c>
       <c r="H128" s="17">
-        <v>0.0035928323441</v>
+        <v>0.0032252366274</v>
       </c>
       <c r="I128" s="16">
-        <v>7.72</v>
+        <v>7.19</v>
       </c>
       <c r="J128" s="11" t="s">
         <v>13</v>
@@ -4969,28 +4876,28 @@
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1">
       <c r="B129" s="12" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D129" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F129" s="15">
         <v>2000</v>
       </c>
       <c r="G129" s="16">
-        <v>9908.21</v>
+        <v>9637.89</v>
       </c>
       <c r="H129" s="17">
-        <v>0.0035832090929</v>
+        <v>0.0032124705942</v>
       </c>
       <c r="I129" s="16">
-        <v>7.69</v>
+        <v>7.18</v>
       </c>
       <c r="J129" s="11" t="s">
         <v>13</v>
@@ -4998,28 +4905,28 @@
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1">
       <c r="B130" s="12" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D130" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E130" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F130" s="15">
         <v>2000</v>
       </c>
       <c r="G130" s="16">
-        <v>9901.05</v>
+        <v>9616.26</v>
       </c>
       <c r="H130" s="17">
-        <v>0.0035806197476</v>
+        <v>0.003205260952</v>
       </c>
       <c r="I130" s="16">
-        <v>7.93</v>
+        <v>7.14</v>
       </c>
       <c r="J130" s="11" t="s">
         <v>13</v>
@@ -5027,28 +4934,28 @@
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1">
       <c r="B131" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D131" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E131" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F131" s="15">
         <v>2000</v>
       </c>
       <c r="G131" s="16">
-        <v>9898.60</v>
+        <v>9615.23</v>
       </c>
       <c r="H131" s="17">
-        <v>0.0035797337286</v>
+        <v>0.0032049176357</v>
       </c>
       <c r="I131" s="16">
-        <v>7.79</v>
+        <v>7.16</v>
       </c>
       <c r="J131" s="11" t="s">
         <v>13</v>
@@ -5056,28 +4963,28 @@
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1">
       <c r="B132" s="12" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D132" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E132" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F132" s="15">
         <v>2000</v>
       </c>
       <c r="G132" s="16">
-        <v>9716.27</v>
+        <v>9577.01</v>
       </c>
       <c r="H132" s="17">
-        <v>0.0035137958333</v>
+        <v>0.0031921782678</v>
       </c>
       <c r="I132" s="16">
-        <v>8.26</v>
+        <v>7.17</v>
       </c>
       <c r="J132" s="11" t="s">
         <v>13</v>
@@ -5085,28 +4992,28 @@
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1">
       <c r="B133" s="12" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D133" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E133" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F133" s="15">
         <v>2000</v>
       </c>
       <c r="G133" s="16">
-        <v>9387.99</v>
+        <v>9571.41</v>
       </c>
       <c r="H133" s="17">
-        <v>0.0033950765206</v>
+        <v>0.0031903116937</v>
       </c>
       <c r="I133" s="16">
-        <v>8.21</v>
+        <v>7.20</v>
       </c>
       <c r="J133" s="11" t="s">
         <v>13</v>
@@ -5114,28 +5021,28 @@
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1">
       <c r="B134" s="12" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D134" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E134" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F134" s="15">
         <v>2000</v>
       </c>
       <c r="G134" s="16">
-        <v>9340.62</v>
+        <v>9507.3</v>
       </c>
       <c r="H134" s="17">
-        <v>0.0033779456145</v>
+        <v>0.0031689427541</v>
       </c>
       <c r="I134" s="16">
-        <v>8.29</v>
+        <v>7.17</v>
       </c>
       <c r="J134" s="11" t="s">
         <v>13</v>
@@ -5143,28 +5050,28 @@
     </row>
     <row r="135" spans="2:10" ht="15" customHeight="1">
       <c r="B135" s="12" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D135" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E135" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F135" s="15">
         <v>2000</v>
       </c>
       <c r="G135" s="16">
-        <v>9281.10</v>
+        <v>9494.98</v>
       </c>
       <c r="H135" s="17">
-        <v>0.0033564207775</v>
+        <v>0.0031648362912</v>
       </c>
       <c r="I135" s="16">
-        <v>8.2</v>
+        <v>6.72</v>
       </c>
       <c r="J135" s="11" t="s">
         <v>13</v>
@@ -5172,28 +5079,28 @@
     </row>
     <row r="136" spans="2:10" ht="15" customHeight="1">
       <c r="B136" s="12" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="C136" s="13" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D136" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E136" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F136" s="15">
         <v>2000</v>
       </c>
       <c r="G136" s="16">
-        <v>9250.31</v>
+        <v>9446.99</v>
       </c>
       <c r="H136" s="17">
-        <v>0.0033452858694</v>
+        <v>0.0031488404183</v>
       </c>
       <c r="I136" s="16">
-        <v>8.53</v>
+        <v>7.17</v>
       </c>
       <c r="J136" s="11" t="s">
         <v>13</v>
@@ -5201,28 +5108,28 @@
     </row>
     <row r="137" spans="2:10" ht="15" customHeight="1">
       <c r="B137" s="12" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="C137" s="13" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="D137" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F137" s="15">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="G137" s="16">
-        <v>8458.91</v>
+        <v>9345.13</v>
       </c>
       <c r="H137" s="17">
-        <v>0.0030590836517</v>
+        <v>0.0031148887696</v>
       </c>
       <c r="I137" s="16">
-        <v>7.71</v>
+        <v>7.21</v>
       </c>
       <c r="J137" s="11" t="s">
         <v>13</v>
@@ -5230,28 +5137,28 @@
     </row>
     <row r="138" spans="2:10" ht="15" customHeight="1">
       <c r="B138" s="12" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="C138" s="13" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="D138" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="F138" s="15">
         <v>1500</v>
       </c>
       <c r="G138" s="16">
-        <v>7482.92</v>
+        <v>7105</v>
       </c>
       <c r="H138" s="17">
-        <v>0.0027061262312</v>
+        <v>0.0023682158202</v>
       </c>
       <c r="I138" s="16">
-        <v>7.58</v>
+        <v>7.12</v>
       </c>
       <c r="J138" s="11" t="s">
         <v>13</v>
@@ -5259,28 +5166,28 @@
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1">
       <c r="B139" s="12" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D139" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F139" s="15">
         <v>1500</v>
       </c>
       <c r="G139" s="16">
-        <v>7440.60</v>
+        <v>7003.05</v>
       </c>
       <c r="H139" s="17">
-        <v>0.0026908216092</v>
+        <v>0.0023342341731</v>
       </c>
       <c r="I139" s="16">
-        <v>7.88</v>
+        <v>7.16</v>
       </c>
       <c r="J139" s="11" t="s">
         <v>13</v>
@@ -5288,28 +5195,28 @@
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1">
       <c r="B140" s="12" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="C140" s="13" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D140" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F140" s="15">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G140" s="16">
-        <v>7427.98</v>
+        <v>4784.19</v>
       </c>
       <c r="H140" s="17">
-        <v>0.0026862577073</v>
+        <v>0.0015946508719</v>
       </c>
       <c r="I140" s="16">
-        <v>7.87</v>
+        <v>7.19</v>
       </c>
       <c r="J140" s="11" t="s">
         <v>13</v>
@@ -5317,28 +5224,28 @@
     </row>
     <row r="141" spans="2:10" ht="15" customHeight="1">
       <c r="B141" s="12" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D141" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F141" s="15">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G141" s="16">
-        <v>7426.42</v>
+        <v>4783.9</v>
       </c>
       <c r="H141" s="17">
-        <v>0.0026856935483</v>
+        <v>0.00159455421</v>
       </c>
       <c r="I141" s="16">
-        <v>7.69</v>
+        <v>7.20</v>
       </c>
       <c r="J141" s="11" t="s">
         <v>13</v>
@@ -5346,28 +5253,28 @@
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1">
       <c r="B142" s="12" t="s">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D142" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F142" s="15">
         <v>1000</v>
       </c>
       <c r="G142" s="16">
-        <v>4995.73</v>
+        <v>4782.1</v>
       </c>
       <c r="H142" s="17">
-        <v>0.0018066578284</v>
+        <v>0.0015939542398</v>
       </c>
       <c r="I142" s="16">
-        <v>7.81</v>
+        <v>7.05</v>
       </c>
       <c r="J142" s="11" t="s">
         <v>13</v>
@@ -5375,28 +5282,28 @@
     </row>
     <row r="143" spans="2:10" ht="15" customHeight="1">
       <c r="B143" s="12" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D143" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F143" s="15">
         <v>1000</v>
       </c>
       <c r="G143" s="16">
-        <v>4993.6</v>
+        <v>4777.29</v>
       </c>
       <c r="H143" s="17">
-        <v>0.0018058875343</v>
+        <v>0.001592350986</v>
       </c>
       <c r="I143" s="16">
-        <v>7.81</v>
+        <v>7.21</v>
       </c>
       <c r="J143" s="11" t="s">
         <v>13</v>
@@ -5404,28 +5311,28 @@
     </row>
     <row r="144" spans="2:10" ht="15" customHeight="1">
       <c r="B144" s="12" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D144" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F144" s="15">
         <v>1000</v>
       </c>
       <c r="G144" s="16">
-        <v>4986.14</v>
+        <v>4740.17</v>
       </c>
       <c r="H144" s="17">
-        <v>0.0018031896969</v>
+        <v>0.0015799782666</v>
       </c>
       <c r="I144" s="16">
-        <v>7.81</v>
+        <v>7.05</v>
       </c>
       <c r="J144" s="11" t="s">
         <v>13</v>
@@ -5433,28 +5340,28 @@
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1">
       <c r="B145" s="12" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D145" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F145" s="15">
         <v>1000</v>
       </c>
       <c r="G145" s="16">
-        <v>4980.80</v>
+        <v>4739.21</v>
       </c>
       <c r="H145" s="17">
-        <v>0.0018012585371</v>
+        <v>0.0015796582825</v>
       </c>
       <c r="I145" s="16">
-        <v>7.41</v>
+        <v>7.05</v>
       </c>
       <c r="J145" s="11" t="s">
         <v>13</v>
@@ -5462,28 +5369,28 @@
     </row>
     <row r="146" spans="2:10" ht="15" customHeight="1">
       <c r="B146" s="12" t="s">
-        <v>208</v>
+        <v>151</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D146" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F146" s="15">
         <v>1000</v>
       </c>
       <c r="G146" s="16">
-        <v>4978.15</v>
+        <v>4738.62</v>
       </c>
       <c r="H146" s="17">
-        <v>0.00180030019</v>
+        <v>0.0015794616256</v>
       </c>
       <c r="I146" s="16">
-        <v>8.01</v>
+        <v>7.17</v>
       </c>
       <c r="J146" s="11" t="s">
         <v>13</v>
@@ -5491,28 +5398,28 @@
     </row>
     <row r="147" spans="2:10" ht="15" customHeight="1">
       <c r="B147" s="12" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="D147" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F147" s="15">
         <v>1000</v>
       </c>
       <c r="G147" s="16">
-        <v>4960.78</v>
+        <v>4725.25</v>
       </c>
       <c r="H147" s="17">
-        <v>0.0017940184962</v>
+        <v>0.0015750051801</v>
       </c>
       <c r="I147" s="16">
-        <v>7.40</v>
+        <v>7.17</v>
       </c>
       <c r="J147" s="11" t="s">
         <v>13</v>
@@ -5520,28 +5427,28 @@
     </row>
     <row r="148" spans="2:10" ht="15" customHeight="1">
       <c r="B148" s="12" t="s">
-        <v>212</v>
+        <v>136</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="D148" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="F148" s="15">
         <v>1000</v>
       </c>
       <c r="G148" s="16">
-        <v>4960.70</v>
+        <v>4674.69</v>
       </c>
       <c r="H148" s="17">
-        <v>0.0017939895649</v>
+        <v>0.001558152683</v>
       </c>
       <c r="I148" s="16">
-        <v>7.82</v>
+        <v>7.16</v>
       </c>
       <c r="J148" s="11" t="s">
         <v>13</v>
@@ -5549,57 +5456,36 @@
     </row>
     <row r="149" spans="2:10" ht="15" customHeight="1">
       <c r="B149" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C149" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="D149" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F149" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G149" s="16">
-        <v>4960.11</v>
-      </c>
-      <c r="H149" s="17">
-        <v>0.0017937761971</v>
-      </c>
-      <c r="I149" s="16">
-        <v>7.72</v>
+        <v>13</v>
       </c>
       <c r="J149" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="150" spans="2:10" ht="15" customHeight="1">
-      <c r="B150" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C150" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="D150" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E150" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F150" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G150" s="16">
-        <v>4957.68</v>
-      </c>
-      <c r="H150" s="17">
-        <v>0.0017928974109</v>
-      </c>
-      <c r="I150" s="16">
-        <v>7.79</v>
+      <c r="B150" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H150" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I150" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J150" s="11" t="s">
         <v>13</v>
@@ -5607,57 +5493,36 @@
     </row>
     <row r="151" spans="2:10" ht="15" customHeight="1">
       <c r="B151" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C151" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D151" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E151" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F151" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G151" s="16">
-        <v>4681.16</v>
-      </c>
-      <c r="H151" s="17">
-        <v>0.0016928966057</v>
-      </c>
-      <c r="I151" s="16">
-        <v>8.21</v>
+        <v>13</v>
       </c>
       <c r="J151" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="152" spans="2:10" ht="15" customHeight="1">
-      <c r="B152" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="C152" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E152" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F152" s="15">
-        <v>1000</v>
-      </c>
-      <c r="G152" s="16">
-        <v>4632.58</v>
-      </c>
-      <c r="H152" s="17">
-        <v>0.0016753281147</v>
-      </c>
-      <c r="I152" s="16">
-        <v>8.3</v>
+      <c r="B152" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152" s="9">
+        <v>301787.56</v>
+      </c>
+      <c r="H152" s="10">
+        <v>0.100590861922</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J152" s="11" t="s">
         <v>13</v>
@@ -5665,28 +5530,28 @@
     </row>
     <row r="153" spans="2:10" ht="15" customHeight="1">
       <c r="B153" s="12" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="C153" s="13" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="D153" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F153" s="15">
-        <v>1000</v>
+        <v>200000000</v>
       </c>
       <c r="G153" s="16">
-        <v>4628.47</v>
+        <v>191651</v>
       </c>
       <c r="H153" s="17">
-        <v>0.0016738417726</v>
+        <v>0.0638804968576</v>
       </c>
       <c r="I153" s="16">
-        <v>8.23</v>
+        <v>5.60</v>
       </c>
       <c r="J153" s="11" t="s">
         <v>13</v>
@@ -5694,28 +5559,28 @@
     </row>
     <row r="154" spans="2:10" ht="15" customHeight="1">
       <c r="B154" s="12" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="C154" s="13" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="D154" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F154" s="15">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="G154" s="16">
-        <v>4624.71</v>
+        <v>47962.10</v>
       </c>
       <c r="H154" s="17">
-        <v>0.0016724820047</v>
+        <v>0.0159865733981</v>
       </c>
       <c r="I154" s="16">
-        <v>8.32</v>
+        <v>5.60</v>
       </c>
       <c r="J154" s="11" t="s">
         <v>13</v>
@@ -5723,28 +5588,28 @@
     </row>
     <row r="155" spans="2:10" ht="15" customHeight="1">
       <c r="B155" s="12" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C155" s="13" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="D155" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F155" s="15">
-        <v>1000</v>
+        <v>50000000</v>
       </c>
       <c r="G155" s="16">
-        <v>4623.16</v>
+        <v>47861.65</v>
       </c>
       <c r="H155" s="17">
-        <v>0.0016719214621</v>
+        <v>0.0159530917262</v>
       </c>
       <c r="I155" s="16">
-        <v>8.53</v>
+        <v>5.60</v>
       </c>
       <c r="J155" s="11" t="s">
         <v>13</v>
@@ -5752,28 +5617,28 @@
     </row>
     <row r="156" spans="2:10" ht="15" customHeight="1">
       <c r="B156" s="12" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="D156" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F156" s="15">
-        <v>500</v>
+        <v>15000000</v>
       </c>
       <c r="G156" s="16">
-        <v>2498.41</v>
+        <v>14312.81</v>
       </c>
       <c r="H156" s="17">
-        <v>0.0009035260082</v>
+        <v>0.0047706999401</v>
       </c>
       <c r="I156" s="16">
-        <v>7.74</v>
+        <v>5.60</v>
       </c>
       <c r="J156" s="11" t="s">
         <v>13</v>
@@ -5781,57 +5646,36 @@
     </row>
     <row r="157" spans="2:10" ht="15" customHeight="1">
       <c r="B157" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C157" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="D157" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E157" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F157" s="15">
-        <v>500</v>
-      </c>
-      <c r="G157" s="16">
-        <v>2479.90</v>
-      </c>
-      <c r="H157" s="17">
-        <v>0.0008968320443</v>
-      </c>
-      <c r="I157" s="16">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J157" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="158" spans="2:10" ht="15" customHeight="1">
-      <c r="B158" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C158" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="D158" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E158" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F158" s="15">
-        <v>500</v>
-      </c>
-      <c r="G158" s="16">
-        <v>2475.06</v>
-      </c>
-      <c r="H158" s="17">
-        <v>0.0008950817047</v>
-      </c>
-      <c r="I158" s="16">
-        <v>8</v>
+      <c r="B158" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="9">
+        <v>7037.93</v>
+      </c>
+      <c r="H158" s="10">
+        <v>0.0023458602629</v>
+      </c>
+      <c r="I158" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J158" s="11" t="s">
         <v>13</v>
@@ -5839,6 +5683,27 @@
     </row>
     <row r="159" spans="2:10" ht="15" customHeight="1">
       <c r="B159" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C159" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="D159" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="F159" s="15">
+        <v>62889.426</v>
+      </c>
+      <c r="G159" s="16">
+        <v>7037.93</v>
+      </c>
+      <c r="H159" s="17">
+        <v>0.0023458602629</v>
+      </c>
+      <c r="I159" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J159" s="11" t="s">
@@ -5846,28 +5711,7 @@
       </c>
     </row>
     <row r="160" spans="2:10" ht="15" customHeight="1">
-      <c r="B160" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C160" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D160" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F160" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G160" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H160" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I160" s="9" t="s">
+      <c r="B160" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J160" s="11" t="s">
@@ -5875,7 +5719,28 @@
       </c>
     </row>
     <row r="161" spans="2:10" ht="15" customHeight="1">
-      <c r="B161" s="12" t="s">
+      <c r="B161" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="9">
+        <v>17393.70</v>
+      </c>
+      <c r="H161" s="10">
+        <v>0.0057976123171</v>
+      </c>
+      <c r="I161" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J161" s="11" t="s">
@@ -5883,28 +5748,7 @@
       </c>
     </row>
     <row r="162" spans="2:10" ht="15" customHeight="1">
-      <c r="B162" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C162" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D162" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E162" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G162" s="9">
-        <v>253489.25</v>
-      </c>
-      <c r="H162" s="10">
-        <v>0.0916719554358</v>
-      </c>
-      <c r="I162" s="9" t="s">
+      <c r="B162" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J162" s="11" t="s">
@@ -5912,482 +5756,163 @@
       </c>
     </row>
     <row r="163" spans="2:10" ht="15" customHeight="1">
-      <c r="B163" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C163" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="D163" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E163" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F163" s="15">
-        <v>95000000</v>
-      </c>
-      <c r="G163" s="16">
-        <v>94451.38</v>
-      </c>
-      <c r="H163" s="17">
-        <v>0.0341574354661</v>
-      </c>
-      <c r="I163" s="16">
-        <v>6.43</v>
-      </c>
-      <c r="J163" s="11" t="s">
+      <c r="B163" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C163" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E163" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" s="19">
+        <v>-59359.08723802958</v>
+      </c>
+      <c r="H163" s="20">
+        <v>-0.019785380643873432</v>
+      </c>
+      <c r="I163" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J163" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="164" spans="2:10" ht="15" customHeight="1">
-      <c r="B164" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C164" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D164" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E164" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F164" s="15">
-        <v>40000000</v>
-      </c>
-      <c r="G164" s="16">
-        <v>39671.8</v>
-      </c>
-      <c r="H164" s="17">
-        <v>0.0143469258821</v>
-      </c>
-      <c r="I164" s="16">
-        <v>6.43</v>
-      </c>
-      <c r="J164" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="165" spans="2:10" ht="15" customHeight="1">
-      <c r="B165" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="C165" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="D165" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E165" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F165" s="15">
-        <v>37500000</v>
-      </c>
-      <c r="G165" s="16">
-        <v>37239.11</v>
-      </c>
-      <c r="H165" s="17">
-        <v>0.0134671668814</v>
-      </c>
-      <c r="I165" s="16">
-        <v>6.39</v>
-      </c>
-      <c r="J165" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="166" spans="2:10" ht="15" customHeight="1">
-      <c r="B166" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="C166" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="D166" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E166" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F166" s="15">
-        <v>25000000</v>
-      </c>
-      <c r="G166" s="16">
-        <v>24942.95</v>
-      </c>
-      <c r="H166" s="17">
-        <v>0.0090203785795</v>
-      </c>
-      <c r="I166" s="16">
-        <v>6.42</v>
-      </c>
-      <c r="J166" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="167" spans="2:10" ht="15" customHeight="1">
-      <c r="B167" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C167" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="D167" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E167" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F167" s="15">
-        <v>25000000</v>
-      </c>
-      <c r="G167" s="16">
-        <v>24886.10</v>
-      </c>
-      <c r="H167" s="17">
-        <v>0.0089998193224</v>
-      </c>
-      <c r="I167" s="16">
-        <v>6.43</v>
-      </c>
-      <c r="J167" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="168" spans="2:10" ht="15" customHeight="1">
-      <c r="B168" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C168" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D168" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E168" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F168" s="15">
-        <v>22500000</v>
-      </c>
-      <c r="G168" s="16">
-        <v>22343.47</v>
-      </c>
-      <c r="H168" s="17">
-        <v>0.0080803015754</v>
-      </c>
-      <c r="I168" s="16">
-        <v>6.39</v>
-      </c>
-      <c r="J168" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="169" spans="2:10" ht="15" customHeight="1">
-      <c r="B169" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="C169" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="D169" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E169" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F169" s="15">
-        <v>10000000</v>
-      </c>
-      <c r="G169" s="16">
-        <v>9954.44</v>
-      </c>
-      <c r="H169" s="17">
-        <v>0.0035999277289</v>
-      </c>
-      <c r="I169" s="16">
-        <v>6.43</v>
-      </c>
-      <c r="J169" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="170" spans="2:10" ht="15" customHeight="1">
-      <c r="B170" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J170" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="171" spans="2:10" ht="15" customHeight="1">
-      <c r="B171" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D171" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F171" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G171" s="9">
-        <v>6861.61</v>
-      </c>
-      <c r="H171" s="10">
-        <v>0.0024814354302</v>
-      </c>
-      <c r="I171" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J171" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="172" spans="2:10" ht="15" customHeight="1">
-      <c r="B172" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="C172" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E172" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="F172" s="15">
-        <v>62889.426</v>
-      </c>
-      <c r="G172" s="16">
-        <v>6861.61</v>
-      </c>
-      <c r="H172" s="17">
-        <v>0.0024814354302</v>
-      </c>
-      <c r="I172" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="J172" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="173" spans="2:10" ht="15" customHeight="1">
-      <c r="B173" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J173" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="174" spans="2:10" ht="15" customHeight="1">
-      <c r="B174" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D174" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E174" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F174" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G174" s="9">
-        <v>57826.42</v>
-      </c>
-      <c r="H174" s="10">
-        <v>0.0209123700404</v>
-      </c>
-      <c r="I174" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J174" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="175" spans="2:10" ht="15" customHeight="1">
-      <c r="B175" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J175" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="176" spans="2:10" ht="15" customHeight="1">
-      <c r="B176" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="C176" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D176" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E176" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F176" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G176" s="19">
-        <v>-53031.616044259164</v>
-      </c>
-      <c r="H176" s="20">
-        <v>-0.019178375188344404</v>
-      </c>
-      <c r="I176" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J176" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="177" spans="2:10" ht="15" customHeight="1">
-      <c r="B177" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="C177" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D177" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E177" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F177" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G177" s="19">
-        <v>2765177.73395574</v>
-      </c>
-      <c r="H177" s="20">
-        <v>0.9999999999928556</v>
-      </c>
-      <c r="I177" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J177" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="180" spans="2:9" ht="15" customHeight="1">
-      <c r="B180" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="C180" s="22"/>
-      <c r="D180" s="22"/>
-      <c r="E180" s="22"/>
-      <c r="F180" s="22"/>
-      <c r="G180" s="22"/>
-      <c r="H180" s="22"/>
-      <c r="I180" s="22"/>
-    </row>
-    <row r="181" spans="2:8" ht="15" customHeight="1">
-      <c r="B181" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="C181" s="22"/>
-      <c r="D181" s="22"/>
-      <c r="E181" s="22"/>
-      <c r="F181" s="22"/>
-      <c r="G181" s="22"/>
-      <c r="H181" s="22"/>
-    </row>
-    <row r="182" spans="2:8" ht="15" customHeight="1">
-      <c r="B182" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="C182" s="22"/>
-      <c r="D182" s="22"/>
-      <c r="E182" s="22"/>
-      <c r="F182" s="22"/>
-      <c r="G182" s="22"/>
-      <c r="H182" s="22"/>
-    </row>
-    <row r="183" spans="2:8" ht="15" customHeight="1">
-      <c r="B183" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="C183" s="22"/>
-      <c r="D183" s="22"/>
-      <c r="E183" s="22"/>
-      <c r="F183" s="22"/>
-      <c r="G183" s="22"/>
-      <c r="H183" s="22"/>
-    </row>
-    <row r="184" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B184" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="C184" s="22"/>
-      <c r="D184" s="22"/>
-      <c r="E184" s="22"/>
-      <c r="F184" s="22"/>
-      <c r="G184" s="22"/>
-      <c r="H184" s="22"/>
-    </row>
-    <row r="185" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B185" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C185" s="22"/>
-      <c r="D185" s="22"/>
-      <c r="E185" s="22"/>
-      <c r="F185" s="22"/>
-      <c r="G185" s="22"/>
-      <c r="H185" s="22"/>
-    </row>
-    <row r="186" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B186" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="C186" s="22"/>
-      <c r="D186" s="22"/>
-      <c r="E186" s="22"/>
-      <c r="F186" s="22"/>
-      <c r="G186" s="22"/>
-      <c r="H186" s="22"/>
-    </row>
-    <row r="189" ht="15">
-      <c r="B189" s="22" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="204" ht="15">
-      <c r="B204" s="22" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="205" ht="15">
-      <c r="B205" s="22" t="s">
-        <v>251</v>
+      <c r="B164" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C164" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="19">
+        <v>3000148.86276197</v>
+      </c>
+      <c r="H164" s="20">
+        <v>0.9999999999935267</v>
+      </c>
+      <c r="I164" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J164" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="2:9" ht="15" customHeight="1">
+      <c r="B167" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C167" s="22"/>
+      <c r="D167" s="22"/>
+      <c r="E167" s="22"/>
+      <c r="F167" s="22"/>
+      <c r="G167" s="22"/>
+      <c r="H167" s="22"/>
+      <c r="I167" s="22"/>
+    </row>
+    <row r="168" spans="2:8" ht="15" customHeight="1">
+      <c r="B168" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="C168" s="22"/>
+      <c r="D168" s="22"/>
+      <c r="E168" s="22"/>
+      <c r="F168" s="22"/>
+      <c r="G168" s="22"/>
+      <c r="H168" s="22"/>
+    </row>
+    <row r="169" spans="2:8" ht="15" customHeight="1">
+      <c r="B169" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C169" s="22"/>
+      <c r="D169" s="22"/>
+      <c r="E169" s="22"/>
+      <c r="F169" s="22"/>
+      <c r="G169" s="22"/>
+      <c r="H169" s="22"/>
+    </row>
+    <row r="170" spans="2:8" ht="15" customHeight="1">
+      <c r="B170" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C170" s="22"/>
+      <c r="D170" s="22"/>
+      <c r="E170" s="22"/>
+      <c r="F170" s="22"/>
+      <c r="G170" s="22"/>
+      <c r="H170" s="22"/>
+    </row>
+    <row r="171" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B171" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="C171" s="22"/>
+      <c r="D171" s="22"/>
+      <c r="E171" s="22"/>
+      <c r="F171" s="22"/>
+      <c r="G171" s="22"/>
+      <c r="H171" s="22"/>
+    </row>
+    <row r="172" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B172" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="C172" s="22"/>
+      <c r="D172" s="22"/>
+      <c r="E172" s="22"/>
+      <c r="F172" s="22"/>
+      <c r="G172" s="22"/>
+      <c r="H172" s="22"/>
+    </row>
+    <row r="173" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B173" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="C173" s="22"/>
+      <c r="D173" s="22"/>
+      <c r="E173" s="22"/>
+      <c r="F173" s="22"/>
+      <c r="G173" s="22"/>
+      <c r="H173" s="22"/>
+    </row>
+    <row r="176" ht="15">
+      <c r="B176" s="22" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="191" ht="15">
+      <c r="B191" s="22" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B182:H182"/>
-    <mergeCell ref="B183:H183"/>
-    <mergeCell ref="B184:H184"/>
-    <mergeCell ref="B185:H185"/>
-    <mergeCell ref="B186:H186"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B180:I180"/>
-    <mergeCell ref="B181:H181"/>
+    <mergeCell ref="B167:I167"/>
+    <mergeCell ref="B168:H168"/>
+    <mergeCell ref="B169:H169"/>
+    <mergeCell ref="B170:H170"/>
+    <mergeCell ref="B171:H171"/>
+    <mergeCell ref="B172:H172"/>
+    <mergeCell ref="B173:H173"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
